--- a/StructureDefinition-openimis-patient.xlsx
+++ b/StructureDefinition-openimis-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17092,7 +17092,7 @@
         <v>82</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>22</v>
@@ -18648,7 +18648,7 @@
         <v>82</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>22</v>
@@ -18766,7 +18766,7 @@
         <v>82</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>22</v>
@@ -20444,7 +20444,7 @@
         <v>82</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>
@@ -20562,7 +20562,7 @@
         <v>82</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>22</v>
@@ -22240,7 +22240,7 @@
         <v>82</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>22</v>
@@ -22358,7 +22358,7 @@
         <v>82</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>22</v>
@@ -22716,7 +22716,7 @@
         <v>82</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>22</v>
@@ -25364,7 +25364,7 @@
         <v>82</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>22</v>
@@ -27412,7 +27412,7 @@
         <v>82</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>22</v>
@@ -29572,7 +29572,7 @@
         <v>82</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>22</v>
@@ -29694,7 +29694,7 @@
         <v>82</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>22</v>
@@ -30056,7 +30056,7 @@
         <v>82</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>22</v>
@@ -30174,7 +30174,7 @@
         <v>82</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>22</v>
@@ -30292,7 +30292,7 @@
         <v>82</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>22</v>
@@ -31012,7 +31012,7 @@
         <v>82</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>22</v>
@@ -31858,7 +31858,7 @@
         <v>82</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>22</v>
@@ -31980,7 +31980,7 @@
         <v>82</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-patient.xlsx
+++ b/StructureDefinition-openimis-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-patient.xlsx
+++ b/StructureDefinition-openimis-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
